--- a/examples/leader_smi/01_prices_leader_smi.xlsx
+++ b/examples/leader_smi/01_prices_leader_smi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Размещение видеоролика на телеканале «НТВ»</t>
+          <t>Размещение видеоролика на телеканале «Россия 24»</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4500</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="6">
@@ -487,16 +487,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Размещение баннера на портале «РИА Новости»</t>
+          <t>Размещение видеоролика на телеканале «НТВ»</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>сутки</t>
+          <t>секунда</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="7">
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Радиоролик на радиостанции «Маяк»</t>
+          <t>Размещение видеоролика на телеканале «Первый канал»</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="8">
@@ -523,16 +523,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Размещение статьи в журнале «Известия»</t>
+          <t>Размещение видеоролика на телеканале «ТНТ»</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>полоса</t>
+          <t>секунда</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30000</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Радиоролик на радиостанции «Эхо Москвы»</t>
+          <t>Размещение видеоролика на телеканале «СТС»</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>950</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Размещение видеоролика на телеканале «Первый канал»</t>
+          <t>Размещение видеоролика на телеканале «Пятница»</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -568,7 +568,781 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Размещение видеоролика на телеканале «Звезда»</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Размещение анонса на телеканале «Россия 1» (прайм-тайм)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Размещение анонса на телеканале «НТВ» (прайм-тайм)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Спонсорский блок «Первый канал» (открытие программы)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Спонсорский блок «НТВ» (закрытие программы)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Радиоролик на радиостанции «Маяк»</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Радиоролик на радиостанции «Эхо Москвы»</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Радиоролик на радиостанции «Авторадио»</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Радиоролик на радиостанции «Дорожное радио»</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Радиоролик на радиостанции «Бизнес FM»</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Спонсорство утреннего шоу на «Авторадио»</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Анонс программы на радиостанции «Маяк»</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Анонс программы на «Эхо Москвы»</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>секунда</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Размещение статьи в журнале «Известия»</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Размещение статьи в газете «Коммерсантъ»</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Размещение статьи в журнале «Эксперт»</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Размещение статьи в журнале «РБК»</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Размещение модуля 1/4 полосы в «Коммерсантъ»</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Размещение модуля 1/2 полосы в «Известиях»</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Размещение пресс-релиза в журнале «Эксперт»</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>полоса</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Размещение баннера на портале «РИА Новости»</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Размещение баннера на портале «Лента.ру»</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Размещение баннера на портале «РБК»</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Размещение публикации в «Яндекс.Дзен»</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Размещение поста в группе «ВКонтакте»</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Размещение поста в Telegram-канале (≥100k подписчиков)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Контекстная реклама в «Яндекс.Директ»</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>6500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Видеореклама на YouTube (pre-roll)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Размещение нативного материала в «РИА Новости»</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>выход</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Размещение на билборде 6×3 (Москва, ТТК)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Размещение на билборде 6×3 (Москва, область)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Размещение на ситилайте (центр Москвы)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Размещение на ситилайте (спальные районы)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Размещение на медиафасаде</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>сутки</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Размещение на остановочном комплексе</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Производство видеоролика 30 сек (стандарт)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ролик</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Производство видеоролика 30 сек (премиум)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ролик</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Производство аудиоролика 30 сек</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ролик</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Адаптация ролика под хронометраж 15 сек</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ролик</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Дизайн макета для печатного издания</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>макет</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Дизайн баннера для интернет-размещения</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>макет</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Аналитический отчёт по итогам кампании</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>отчёт</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Медиапланирование рекламной кампании</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>план</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>65000</v>
       </c>
     </row>
   </sheetData>
